--- a/frontend/public/assets/simplefile/department.xlsx
+++ b/frontend/public/assets/simplefile/department.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -29,37 +29,10 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">HR</t>
+    <t xml:space="preserve">aaaaaaaaaaaaa</t>
   </si>
   <si>
     <t xml:space="preserve">success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aaaaaaaaaaaaa</t>
   </si>
 </sst>
 </file>
@@ -157,76 +130,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="8.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -261,7 +179,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>3</v>

--- a/frontend/public/assets/simplefile/department.xlsx
+++ b/frontend/public/assets/simplefile/department.xlsx
@@ -21,7 +21,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t xml:space="preserve">Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -131,7 +137,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.74"/>
@@ -171,18 +177,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/assets/simplefile/department.xlsx
+++ b/frontend/public/assets/simplefile/department.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Departments" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,24 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
   <si>
     <t xml:space="preserve">Department</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aaaaaaaaaaaaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">success</t>
   </si>
 </sst>
 </file>
@@ -114,8 +102,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -137,7 +129,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.74"/>
@@ -169,26 +161,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C2"/>
-  <sheetFormatPr defaultColWidth="8.37890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.37890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
